--- a/Tablas_MH2026.xlsx
+++ b/Tablas_MH2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pablo\Downloads\Ing.Informatica\Tercer Curso\Primer Cuatri\Meta\Practicas\Practica1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2030D8D-BDB9-4022-9745-97E5EC173B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2699788-6F28-4F42-BEC4-7037DFACBF84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -804,7 +804,8 @@
     <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.6640625" bestFit="1" customWidth="1"/>
@@ -1320,8 +1321,12 @@
       <c r="E19" s="17">
         <v>0.21149999999999999</v>
       </c>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
+      <c r="F19" s="17">
+        <v>51649788.170000002</v>
+      </c>
+      <c r="G19" s="17">
+        <v>109988455.09999999</v>
+      </c>
       <c r="H19" s="17">
         <v>603251.89</v>
       </c>
@@ -1357,11 +1362,11 @@
       </c>
       <c r="F20" s="18">
         <f>AVERAGE((F17-G$3)/G$3,(F18-G$3)/G$3,(F19-G$3)/G$3)</f>
-        <v>51.76828478277266</v>
+        <v>78.450836115252557</v>
       </c>
       <c r="G20" s="19">
         <f>AVERAGE(G17:G19)</f>
-        <v>110690.89199999999</v>
+        <v>36736612.294666663</v>
       </c>
       <c r="H20" s="18">
         <f>AVERAGE((H17-I$3)/I$3,(H18-I$3)/I$3,(H19-I$3)/I$3)</f>
@@ -1402,11 +1407,11 @@
       </c>
       <c r="F21" s="19">
         <f>STDEV((F17-G$3)/G$3,(F18-G$3)/G$3,(F19-G$3)/G$3)</f>
-        <v>45.69904373978946</v>
+        <v>0.54848266400633539</v>
       </c>
       <c r="G21" s="19">
         <f>STDEV(G17:G19)</f>
-        <v>1196.7567311120813</v>
+        <v>63437956.749087222</v>
       </c>
       <c r="H21" s="19">
         <f>STDEV((H17-I$3)/I$3,(H18-I$3)/I$3,(H19-I$3)/I$3)</f>
@@ -1871,11 +1876,11 @@
       </c>
       <c r="F52" s="3">
         <f>F20</f>
-        <v>51.76828478277266</v>
+        <v>78.450836115252557</v>
       </c>
       <c r="G52" s="3">
         <f>G20</f>
-        <v>110690.89199999999</v>
+        <v>36736612.294666663</v>
       </c>
       <c r="H52" s="3">
         <f>H20</f>
@@ -1895,11 +1900,11 @@
       </c>
       <c r="L52" s="8">
         <f>AVERAGE(B52,D52,F52,H52,J52)</f>
-        <v>20.691151022961638</v>
+        <v>26.027661289457619</v>
       </c>
       <c r="M52" s="8">
         <f>AVERAGE(C52,E52,G52,I52,K52)</f>
-        <v>22140.837566666662</v>
+        <v>7347325.1181000005</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">

--- a/Tablas_MH2026.xlsx
+++ b/Tablas_MH2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pablo\Downloads\Ing.Informatica\Tercer Curso\Primer Cuatri\Meta\Practicas\Practica1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2699788-6F28-4F42-BEC4-7037DFACBF84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E277C6-A4F2-4D14-8EF8-8F9B53CDD7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -544,24 +544,30 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -572,12 +578,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -813,29 +813,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="21" t="s">
+      <c r="C1" s="24"/>
+      <c r="D1" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="21" t="s">
+      <c r="E1" s="24"/>
+      <c r="F1" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="21" t="s">
+      <c r="G1" s="24"/>
+      <c r="H1" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="22"/>
-      <c r="J1" s="21" t="s">
+      <c r="I1" s="24"/>
+      <c r="J1" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="22"/>
+      <c r="K1" s="24"/>
     </row>
     <row r="2" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="25" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="13" t="s">
@@ -870,66 +870,66 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="24"/>
-      <c r="B3" s="23" t="s">
+      <c r="A3" s="22"/>
+      <c r="B3" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="27">
         <v>2579</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E3" s="27">
         <v>6110</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="25">
+      <c r="G3" s="27">
         <v>645238</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="27">
         <v>58537</v>
       </c>
-      <c r="J3" s="23" t="s">
+      <c r="J3" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="27">
         <v>224094</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
     </row>
     <row r="5" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="24"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="22"/>
     </row>
     <row r="6" spans="1:11" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="24"/>
+      <c r="A6" s="22"/>
       <c r="B6" s="16" t="s">
         <v>1</v>
       </c>
@@ -966,34 +966,34 @@
         <v>4</v>
       </c>
       <c r="B7" s="17">
-        <v>3316.97</v>
+        <v>30296.82</v>
       </c>
       <c r="C7" s="17">
-        <v>3.0019</v>
+        <v>0</v>
       </c>
       <c r="D7" s="17">
-        <v>7216.17</v>
+        <v>40397.47</v>
       </c>
       <c r="E7" s="17">
-        <v>0.7429</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="F7" s="17">
-        <v>789589.35</v>
+        <v>51161687.810000002</v>
       </c>
       <c r="G7" s="17">
-        <v>197804.39379999999</v>
+        <v>234665.56880000001</v>
       </c>
       <c r="H7" s="17">
-        <v>64161.47</v>
+        <v>640770.88</v>
       </c>
       <c r="I7" s="17">
-        <v>1.0206999999999999</v>
+        <v>0.30349999999999999</v>
       </c>
       <c r="J7" s="17">
-        <v>287467.5</v>
+        <v>5670064.4900000002</v>
       </c>
       <c r="K7" s="17">
-        <v>51.970700000000001</v>
+        <v>15.7926</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
@@ -1002,43 +1002,43 @@
       </c>
       <c r="B8" s="18">
         <f>AVERAGE((B7-C$3)/C$3)</f>
-        <v>0.28614579294300108</v>
+        <v>10.747506785575805</v>
       </c>
       <c r="C8" s="19">
         <f>AVERAGE(C7:C7)</f>
-        <v>3.0019</v>
+        <v>0</v>
       </c>
       <c r="D8" s="18">
         <f>AVERAGE((D7-E$3)/E$3)</f>
-        <v>0.18104255319148937</v>
+        <v>5.6116972176759417</v>
       </c>
       <c r="E8" s="19">
         <f>AVERAGE(E7:E7)</f>
-        <v>0.7429</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="F8" s="18">
         <f>AVERAGE((F7-G$3)/G$3)</f>
-        <v>0.22371799243069995</v>
+        <v>78.291188383201245</v>
       </c>
       <c r="G8" s="19">
         <f>AVERAGE(G7:G7)</f>
-        <v>197804.39379999999</v>
+        <v>234665.56880000001</v>
       </c>
       <c r="H8" s="18">
         <f>AVERAGE((H7-I$3)/I$3)</f>
-        <v>9.608401523822542E-2</v>
+        <v>9.9464249961562778</v>
       </c>
       <c r="I8" s="19">
         <f>AVERAGE(I7:I7)</f>
-        <v>1.0206999999999999</v>
+        <v>0.30349999999999999</v>
       </c>
       <c r="J8" s="18">
         <f>AVERAGE((J7-K$3)/K$3)</f>
-        <v>0.28279873624461166</v>
+        <v>24.302170026863728</v>
       </c>
       <c r="K8" s="19">
         <f>AVERAGE(K7:K7)</f>
-        <v>51.970700000000001</v>
+        <v>15.7926</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
@@ -1087,29 +1087,29 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="21" t="s">
+      <c r="C11" s="24"/>
+      <c r="D11" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="22"/>
-      <c r="F11" s="21" t="s">
+      <c r="E11" s="24"/>
+      <c r="F11" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="22"/>
-      <c r="H11" s="21" t="s">
+      <c r="G11" s="24"/>
+      <c r="H11" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="22"/>
-      <c r="J11" s="21" t="s">
+      <c r="I11" s="24"/>
+      <c r="J11" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="K11" s="22"/>
+      <c r="K11" s="24"/>
     </row>
     <row r="12" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="25" t="s">
         <v>21</v>
       </c>
       <c r="B12" s="13" t="s">
@@ -1144,66 +1144,66 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="24"/>
-      <c r="B13" s="23" t="s">
+      <c r="A13" s="22"/>
+      <c r="B13" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="27">
         <v>2579</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="27">
         <v>6110</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="27">
         <v>645238</v>
       </c>
-      <c r="H13" s="23" t="s">
+      <c r="H13" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="27">
         <v>58537</v>
       </c>
-      <c r="J13" s="23" t="s">
+      <c r="J13" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="27">
         <v>224094</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="24"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
     </row>
     <row r="15" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="24"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="24"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="22"/>
     </row>
     <row r="16" spans="1:11" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="24"/>
+      <c r="A16" s="22"/>
       <c r="B16" s="16" t="s">
         <v>1</v>
       </c>
@@ -1431,29 +1431,29 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="21" t="s">
+      <c r="C23" s="24"/>
+      <c r="D23" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="22"/>
-      <c r="F23" s="21" t="s">
+      <c r="E23" s="24"/>
+      <c r="F23" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="22"/>
-      <c r="H23" s="21" t="s">
+      <c r="G23" s="24"/>
+      <c r="H23" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="I23" s="22"/>
-      <c r="J23" s="21" t="s">
+      <c r="I23" s="24"/>
+      <c r="J23" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="K23" s="22"/>
+      <c r="K23" s="24"/>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="25" t="s">
         <v>22</v>
       </c>
       <c r="B24" s="13" t="s">
@@ -1488,66 +1488,66 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="24"/>
-      <c r="B25" s="23" t="s">
+      <c r="A25" s="22"/>
+      <c r="B25" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="27">
         <v>2579</v>
       </c>
-      <c r="D25" s="23" t="s">
+      <c r="D25" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="25">
+      <c r="E25" s="27">
         <v>6110</v>
       </c>
-      <c r="F25" s="23" t="s">
+      <c r="F25" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="G25" s="25">
+      <c r="G25" s="27">
         <v>645238</v>
       </c>
-      <c r="H25" s="23" t="s">
+      <c r="H25" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="I25" s="25">
+      <c r="I25" s="27">
         <v>58537</v>
       </c>
-      <c r="J25" s="23" t="s">
+      <c r="J25" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="K25" s="25">
+      <c r="K25" s="27">
         <v>224094</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="24"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="24"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="24"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="22"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="24"/>
+      <c r="A28" s="22"/>
       <c r="B28" s="16" t="s">
         <v>1</v>
       </c>
@@ -1583,46 +1583,106 @@
       <c r="A29" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
+      <c r="B29" s="17">
+        <v>13636.36</v>
+      </c>
+      <c r="C29" s="17">
+        <v>9.5574999999999992</v>
+      </c>
+      <c r="D29" s="17">
+        <v>14260.8</v>
+      </c>
+      <c r="E29" s="17">
+        <v>6.3170999999999999</v>
+      </c>
+      <c r="F29" s="17">
+        <v>51394136.049999997</v>
+      </c>
+      <c r="G29" s="17">
+        <v>173436.6257</v>
+      </c>
+      <c r="H29" s="17">
+        <v>225651.23</v>
+      </c>
+      <c r="I29" s="17">
+        <v>10.911899999999999</v>
+      </c>
+      <c r="J29" s="17">
+        <v>3483130.73</v>
+      </c>
+      <c r="K29" s="17">
+        <v>34.001399999999997</v>
+      </c>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
+      <c r="B30" s="17">
+        <v>13178.49</v>
+      </c>
+      <c r="C30" s="17">
+        <v>9.2847000000000008</v>
+      </c>
+      <c r="D30" s="17">
+        <v>15545.3</v>
+      </c>
+      <c r="E30" s="17">
+        <v>7.1111000000000004</v>
+      </c>
+      <c r="F30" s="17">
+        <v>50743744.5</v>
+      </c>
+      <c r="G30" s="17">
+        <v>164031.9927</v>
+      </c>
+      <c r="H30" s="17">
+        <v>265243.32</v>
+      </c>
+      <c r="I30" s="17">
+        <v>14.889200000000001</v>
+      </c>
+      <c r="J30" s="17">
+        <v>3401755.73</v>
+      </c>
+      <c r="K30" s="17">
+        <v>43.829000000000001</v>
+      </c>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
+      <c r="B31" s="17">
+        <v>14191.92</v>
+      </c>
+      <c r="C31" s="17">
+        <v>6.4379999999999997</v>
+      </c>
+      <c r="D31" s="17">
+        <v>16510.27</v>
+      </c>
+      <c r="E31" s="17">
+        <v>6.0346000000000002</v>
+      </c>
+      <c r="F31" s="17">
+        <v>50962909.799999997</v>
+      </c>
+      <c r="G31" s="17">
+        <v>182635.92929999999</v>
+      </c>
+      <c r="H31" s="17">
+        <v>277422.81</v>
+      </c>
+      <c r="I31" s="17">
+        <v>17.801300000000001</v>
+      </c>
+      <c r="J31" s="17">
+        <v>3538871.8</v>
+      </c>
+      <c r="K31" s="17">
+        <v>40.497799999999998</v>
+      </c>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="15" t="s">
@@ -1630,43 +1690,43 @@
       </c>
       <c r="B32" s="18">
         <f>AVERAGE((B29-C$3)/C$3,(B30-C$3)/C$3,(B31-C$3)/C$3)</f>
-        <v>-1</v>
-      </c>
-      <c r="C32" s="19" t="e">
+        <v>4.3000865968721724</v>
+      </c>
+      <c r="C32" s="19">
         <f>AVERAGE(C29:C31)</f>
-        <v>#DIV/0!</v>
+        <v>8.426733333333333</v>
       </c>
       <c r="D32" s="18">
         <f>AVERAGE((D29-E$3)/E$3,(D30-E$3)/E$3,(D31-E$3)/E$3)</f>
-        <v>-1</v>
-      </c>
-      <c r="E32" s="19" t="e">
+        <v>1.5268068739770868</v>
+      </c>
+      <c r="E32" s="19">
         <f>AVERAGE(E29:E31)</f>
-        <v>#DIV/0!</v>
+        <v>6.4876000000000005</v>
       </c>
       <c r="F32" s="18">
         <f>AVERAGE((F29-G$3)/G$3,(F30-G$3)/G$3,(F31-G$3)/G$3)</f>
-        <v>-1</v>
-      </c>
-      <c r="G32" s="19" t="e">
+        <v>78.09267089559718</v>
+      </c>
+      <c r="G32" s="19">
         <f>AVERAGE(G29:G31)</f>
-        <v>#DIV/0!</v>
+        <v>173368.18256666666</v>
       </c>
       <c r="H32" s="18">
         <f>AVERAGE((H29-I$3)/I$3,(H30-I$3)/I$3,(H31-I$3)/I$3)</f>
-        <v>-1</v>
-      </c>
-      <c r="I32" s="19" t="e">
+        <v>3.3751095318630386</v>
+      </c>
+      <c r="I32" s="19">
         <f>AVERAGE(I29:I31)</f>
-        <v>#DIV/0!</v>
+        <v>14.534133333333335</v>
       </c>
       <c r="J32" s="18">
         <f>AVERAGE((J29-K$3)/K$3,(J30-K$3)/K$3,(J31-K$3)/K$3)</f>
-        <v>-1</v>
-      </c>
-      <c r="K32" s="19" t="e">
+        <v>14.505038451126163</v>
+      </c>
+      <c r="K32" s="19">
         <f>AVERAGE(K29:K31)</f>
-        <v>#DIV/0!</v>
+        <v>39.442733333333329</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1675,43 +1735,43 @@
       </c>
       <c r="B33" s="19">
         <f>STDEV((B29-C$3)/C$3,(B30-C$3)/C$3,(B31-C$3)/C$3)</f>
-        <v>0</v>
-      </c>
-      <c r="C33" s="19" t="e">
+        <v>0.19678136186461742</v>
+      </c>
+      <c r="C33" s="19">
         <f>STDEV(C29:C31)</f>
-        <v>#DIV/0!</v>
+        <v>1.7276863613901003</v>
       </c>
       <c r="D33" s="19">
         <f>STDEV((D29-E$3)/E$3,(D30-E$3)/E$3,(D31-E$3)/E$3)</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="19" t="e">
+        <v>0.18469902004665073</v>
+      </c>
+      <c r="E33" s="19">
         <f>STDEV(E29:E31)</f>
-        <v>#DIV/0!</v>
+        <v>0.55813596013874633</v>
       </c>
       <c r="F33" s="19">
         <f>STDEV((F29-G$3)/G$3,(F30-G$3)/G$3,(F31-G$3)/G$3)</f>
-        <v>0</v>
-      </c>
-      <c r="G33" s="19" t="e">
+        <v>0.51284566107356222</v>
+      </c>
+      <c r="G33" s="19">
         <f>STDEV(G29:G31)</f>
-        <v>#DIV/0!</v>
+        <v>9302.157147730848</v>
       </c>
       <c r="H33" s="19">
         <f>STDEV((H29-I$3)/I$3,(H30-I$3)/I$3,(H31-I$3)/I$3)</f>
-        <v>0</v>
-      </c>
-      <c r="I33" s="19" t="e">
+        <v>0.46241419329654254</v>
+      </c>
+      <c r="I33" s="19">
         <f>STDEV(I29:I31)</f>
-        <v>#DIV/0!</v>
+        <v>3.4583973663148275</v>
       </c>
       <c r="J33" s="19">
         <f>STDEV((J29-K$3)/K$3,(J30-K$3)/K$3,(J31-K$3)/K$3)</f>
-        <v>0</v>
-      </c>
-      <c r="K33" s="19" t="e">
+        <v>0.3077112064957051</v>
+      </c>
+      <c r="K33" s="19">
         <f>STDEV(K29:K31)</f>
-        <v>#DIV/0!</v>
+        <v>4.998030081275366</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -1736,34 +1796,34 @@
     <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="48" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="49" spans="1:13" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="30"/>
-      <c r="B49" s="32" t="s">
+      <c r="A49" s="32"/>
+      <c r="B49" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="33"/>
-      <c r="D49" s="27" t="s">
+      <c r="C49" s="35"/>
+      <c r="D49" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E49" s="28"/>
-      <c r="F49" s="34" t="s">
+      <c r="E49" s="29"/>
+      <c r="F49" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="G49" s="33"/>
-      <c r="H49" s="27" t="s">
+      <c r="G49" s="35"/>
+      <c r="H49" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="I49" s="28"/>
-      <c r="J49" s="27" t="s">
+      <c r="I49" s="29"/>
+      <c r="J49" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="K49" s="28"/>
-      <c r="L49" s="35" t="s">
+      <c r="K49" s="29"/>
+      <c r="L49" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="M49" s="36"/>
+      <c r="M49" s="31"/>
     </row>
     <row r="50" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="31"/>
+      <c r="A50" s="33"/>
       <c r="B50" s="12" t="s">
         <v>20</v>
       </c>
@@ -1806,52 +1866,52 @@
         <v>11</v>
       </c>
       <c r="B51" s="3">
-        <f>B8</f>
-        <v>0.28614579294300108</v>
+        <f t="shared" ref="B51:K51" si="0">B8</f>
+        <v>10.747506785575805</v>
       </c>
       <c r="C51" s="3">
-        <f>C8</f>
-        <v>3.0019</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="D51" s="3">
-        <f>D8</f>
-        <v>0.18104255319148937</v>
+        <f t="shared" si="0"/>
+        <v>5.6116972176759417</v>
       </c>
       <c r="E51" s="3">
-        <f>E8</f>
-        <v>0.7429</v>
+        <f t="shared" si="0"/>
+        <v>0.99399999999999999</v>
       </c>
       <c r="F51" s="3">
-        <f>F8</f>
-        <v>0.22371799243069995</v>
+        <f t="shared" si="0"/>
+        <v>78.291188383201245</v>
       </c>
       <c r="G51" s="3">
-        <f>G8</f>
-        <v>197804.39379999999</v>
+        <f t="shared" si="0"/>
+        <v>234665.56880000001</v>
       </c>
       <c r="H51" s="3">
-        <f>H8</f>
-        <v>9.608401523822542E-2</v>
+        <f t="shared" si="0"/>
+        <v>9.9464249961562778</v>
       </c>
       <c r="I51" s="3">
-        <f>I8</f>
-        <v>1.0206999999999999</v>
+        <f t="shared" si="0"/>
+        <v>0.30349999999999999</v>
       </c>
       <c r="J51" s="3">
-        <f>J8</f>
-        <v>0.28279873624461166</v>
+        <f t="shared" si="0"/>
+        <v>24.302170026863728</v>
       </c>
       <c r="K51" s="3">
-        <f>K8</f>
-        <v>51.970700000000001</v>
+        <f t="shared" si="0"/>
+        <v>15.7926</v>
       </c>
       <c r="L51" s="8">
         <f>AVERAGE(B51,D51,F51,H51,J51)</f>
-        <v>0.21395781800960548</v>
+        <v>25.779797481894597</v>
       </c>
       <c r="M51" s="8">
         <f>AVERAGE(C51,E51,G51,I51,K51)</f>
-        <v>39572.225999999995</v>
+        <v>46936.531780000005</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1859,43 +1919,43 @@
         <v>21</v>
       </c>
       <c r="B52" s="3">
-        <f>B20</f>
+        <f t="shared" ref="B52:K52" si="1">B20</f>
         <v>11.095469820343803</v>
       </c>
       <c r="C52" s="3">
-        <f>C20</f>
+        <f t="shared" si="1"/>
         <v>1.0012999999999999</v>
       </c>
       <c r="D52" s="3">
-        <f>D20</f>
+        <f t="shared" si="1"/>
         <v>5.957828696126569</v>
       </c>
       <c r="E52" s="3">
-        <f>E20</f>
+        <f t="shared" si="1"/>
         <v>0.20926666666666668</v>
       </c>
       <c r="F52" s="3">
-        <f>F20</f>
+        <f t="shared" si="1"/>
         <v>78.450836115252557</v>
       </c>
       <c r="G52" s="3">
-        <f>G20</f>
+        <f t="shared" si="1"/>
         <v>36736612.294666663</v>
       </c>
       <c r="H52" s="3">
-        <f>H20</f>
+        <f t="shared" si="1"/>
         <v>10.74698207971027</v>
       </c>
       <c r="I52" s="3">
-        <f>I20</f>
+        <f t="shared" si="1"/>
         <v>0.25459999999999999</v>
       </c>
       <c r="J52" s="3">
-        <f>J20</f>
+        <f t="shared" si="1"/>
         <v>23.887189735854893</v>
       </c>
       <c r="K52" s="3">
-        <f>K20</f>
+        <f t="shared" si="1"/>
         <v>11.830666666666666</v>
       </c>
       <c r="L52" s="8">
@@ -2886,6 +2946,60 @@
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
     <mergeCell ref="H27:I27"/>
     <mergeCell ref="J27:K27"/>
     <mergeCell ref="H23:I23"/>
@@ -2902,60 +3016,6 @@
     <mergeCell ref="J25:J26"/>
     <mergeCell ref="K25:K26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J49:K49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Tablas_MH2026.xlsx
+++ b/Tablas_MH2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pablo\Downloads\Ing.Informatica\Tercer Curso\Primer Cuatri\Meta\Practicas\Practica1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E277C6-A4F2-4D14-8EF8-8F9B53CDD7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3A3124-E89D-4327-8577-C37359C6A74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="24">
   <si>
     <t>Tamaño</t>
   </si>
@@ -73,12 +73,6 @@
     <t>Greedy</t>
   </si>
   <si>
-    <t>TABU</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
     <t>A280</t>
   </si>
   <si>
@@ -105,12 +99,21 @@
   <si>
     <t>Busqueda Local</t>
   </si>
+  <si>
+    <t>Busqueda Tabú</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>Tabú</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -193,6 +196,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -226,7 +235,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -480,11 +489,83 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -511,9 +592,6 @@
     <xf numFmtId="2" fontId="6" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -535,30 +613,58 @@
     <xf numFmtId="2" fontId="6" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -568,6 +674,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -800,1212 +909,1619 @@
   <cols>
     <col min="1" max="1" width="16.77734375" customWidth="1"/>
     <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="28" width="10.44140625" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" customWidth="1"/>
+    <col min="13" max="13" width="12.77734375" customWidth="1"/>
+    <col min="14" max="28" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="36"/>
+      <c r="F1" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="36"/>
+      <c r="H1" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="23" t="s">
+      <c r="I1" s="36"/>
+      <c r="J1" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="36"/>
+    </row>
+    <row r="2" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="13">
+        <v>280</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="13">
+        <v>130</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="13">
+        <v>18512</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="13">
+        <v>144</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="13">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32"/>
+      <c r="B3" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="24"/>
-      <c r="H1" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="24"/>
-    </row>
-    <row r="2" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="C3" s="33">
+        <v>2579</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="33">
+        <v>6110</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="33">
+        <v>645238</v>
+      </c>
+      <c r="H3" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="33">
+        <v>58537</v>
+      </c>
+      <c r="J3" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="33">
+        <v>224094</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+    </row>
+    <row r="5" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="32"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="32"/>
+    </row>
+    <row r="6" spans="1:11" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="32"/>
+      <c r="B6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="16">
+        <v>30296.82</v>
+      </c>
+      <c r="C7" s="16">
         <v>0</v>
       </c>
-      <c r="C2" s="14">
-        <v>280</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="14">
-        <v>130</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="14">
-        <v>18512</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="I2" s="14">
-        <v>144</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="14">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="22"/>
-      <c r="B3" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="27">
-        <v>2579</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="27">
-        <v>6110</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="27">
-        <v>645238</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="27">
-        <v>58537</v>
-      </c>
-      <c r="J3" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="27">
-        <v>224094</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-    </row>
-    <row r="5" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="22"/>
-    </row>
-    <row r="6" spans="1:11" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
-      <c r="B6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="15" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="17">
-        <v>30296.82</v>
-      </c>
-      <c r="C7" s="17">
-        <v>0</v>
-      </c>
-      <c r="D7" s="17">
+      <c r="D7" s="16">
         <v>40397.47</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="16">
         <v>0.99399999999999999</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="16">
         <v>51161687.810000002</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="16">
         <v>234665.56880000001</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="16">
         <v>640770.88</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="16">
         <v>0.30349999999999999</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="16">
         <v>5670064.4900000002</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="16">
         <v>15.7926</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="17">
         <f>AVERAGE((B7-C$3)/C$3)</f>
         <v>10.747506785575805</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="17">
         <f>AVERAGE(C7:C7)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <f>AVERAGE((D7-E$3)/E$3)</f>
         <v>5.6116972176759417</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="17">
         <f>AVERAGE(E7:E7)</f>
         <v>0.99399999999999999</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <f>AVERAGE((F7-G$3)/G$3)</f>
         <v>78.291188383201245</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="17">
         <f>AVERAGE(G7:G7)</f>
         <v>234665.56880000001</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="17">
         <f>AVERAGE((H7-I$3)/I$3)</f>
         <v>9.9464249961562778</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="17">
         <f>AVERAGE(I7:I7)</f>
         <v>0.30349999999999999</v>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="17">
         <f>AVERAGE((J7-K$3)/K$3)</f>
         <v>24.302170026863728</v>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="17">
         <f>AVERAGE(K7:K7)</f>
         <v>15.7926</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="19" t="e">
+      <c r="B9" s="17" t="e">
         <f>STDEV((B7-C$3)/C$3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C9" s="19" t="e">
+      <c r="C9" s="17" t="e">
         <f>STDEV(C7:C7)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D9" s="19" t="e">
+      <c r="D9" s="17" t="e">
         <f>STDEV((D7-E$3)/E$3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E9" s="19" t="e">
+      <c r="E9" s="17" t="e">
         <f>STDEV(E7:E7)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F9" s="19" t="e">
+      <c r="F9" s="17" t="e">
         <f>STDEV((F7-G$3)/G$3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G9" s="19" t="e">
+      <c r="G9" s="17" t="e">
         <f>STDEV(G7:G7)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H9" s="19" t="e">
+      <c r="H9" s="17" t="e">
         <f>STDEV((H7-I$3)/I$3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I9" s="19" t="e">
+      <c r="I9" s="17" t="e">
         <f>STDEV(I7:I7)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J9" s="19" t="e">
+      <c r="J9" s="17" t="e">
         <f>STDEV((J7-K$3)/K$3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K9" s="19" t="e">
+      <c r="K9" s="17" t="e">
         <f>STDEV(K7:K7)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="36"/>
+      <c r="D11" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="36"/>
+      <c r="F11" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="36"/>
+      <c r="H11" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="24"/>
-      <c r="F11" s="23" t="s">
+      <c r="I11" s="36"/>
+      <c r="J11" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="36"/>
+    </row>
+    <row r="12" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="13">
+        <v>280</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13">
+        <v>130</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
+        <v>18512</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13">
+        <v>144</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="K12" s="13">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="32"/>
+      <c r="B13" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="24"/>
-      <c r="H11" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="24"/>
-      <c r="J11" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11" s="24"/>
-    </row>
-    <row r="12" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="14">
-        <v>280</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="E12" s="14">
-        <v>130</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" s="14">
-        <v>18512</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="I12" s="14">
-        <v>144</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="K12" s="14">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22"/>
-      <c r="B13" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="27">
+      <c r="C13" s="33">
         <v>2579</v>
       </c>
-      <c r="D13" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="27">
+      <c r="D13" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="33">
         <v>6110</v>
       </c>
-      <c r="F13" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="27">
+      <c r="F13" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="33">
         <v>645238</v>
       </c>
-      <c r="H13" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" s="27">
+      <c r="H13" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="33">
         <v>58537</v>
       </c>
-      <c r="J13" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="27">
+      <c r="J13" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" s="33">
         <v>224094</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
     </row>
     <row r="15" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="22"/>
+      <c r="A15" s="32"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="32"/>
     </row>
     <row r="16" spans="1:11" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
-      <c r="B16" s="16" t="s">
+      <c r="A16" s="32"/>
+      <c r="B16" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H16" s="16" t="s">
+      <c r="H16" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J16" s="16" t="s">
+      <c r="J16" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="K16" s="15" t="s">
+      <c r="K16" s="14" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="16">
         <v>32022.14</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="16">
         <v>1.4481999999999999</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="16">
         <v>41067.82</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="16">
         <v>0.21149999999999999</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="16">
         <v>50953722.229999997</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="16">
         <v>109844.6572</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="16">
         <v>755342.33</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="16">
         <v>0.25030000000000002</v>
       </c>
-      <c r="J17" s="17">
+      <c r="J17" s="16">
         <v>5543598.1699999999</v>
       </c>
-      <c r="K17" s="17">
+      <c r="K17" s="16">
         <v>12.714600000000001</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="16">
         <v>29737.78</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="16">
         <v>0.80279999999999996</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="16">
         <v>42695.9</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="16">
         <v>0.20480000000000001</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="16">
         <v>51190585.380000003</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="16">
         <v>111537.1268</v>
       </c>
-      <c r="H18" s="17">
+      <c r="H18" s="16">
         <v>704305.05</v>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="16">
         <v>0.25340000000000001</v>
       </c>
-      <c r="J18" s="17">
+      <c r="J18" s="16">
         <v>5613886.1699999999</v>
       </c>
-      <c r="K18" s="17">
+      <c r="K18" s="16">
         <v>10.8314</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="16">
         <v>31822.73</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="16">
         <v>0.75290000000000001</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="16">
         <v>43773.279999999999</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="16">
         <v>0.21149999999999999</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="16">
         <v>51649788.170000002</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="16">
         <v>109988455.09999999</v>
       </c>
-      <c r="H19" s="17">
+      <c r="H19" s="16">
         <v>603251.89</v>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="16">
         <v>0.2601</v>
       </c>
-      <c r="J19" s="17">
+      <c r="J19" s="16">
         <v>5573725.3499999996</v>
       </c>
-      <c r="K19" s="17">
+      <c r="K19" s="16">
         <v>11.946</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="17">
         <f>AVERAGE((B17-C$3)/C$3,(B18-C$3)/C$3,(B19-C$3)/C$3)</f>
         <v>11.095469820343803</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="17">
         <f>AVERAGE(C17:C19)</f>
         <v>1.0012999999999999</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="17">
         <f>AVERAGE((D17-E$3)/E$3,(D18-E$3)/E$3,(D19-E$3)/E$3)</f>
         <v>5.957828696126569</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="17">
         <f>AVERAGE(E17:E19)</f>
         <v>0.20926666666666668</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="17">
         <f>AVERAGE((F17-G$3)/G$3,(F18-G$3)/G$3,(F19-G$3)/G$3)</f>
         <v>78.450836115252557</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="17">
         <f>AVERAGE(G17:G19)</f>
         <v>36736612.294666663</v>
       </c>
-      <c r="H20" s="18">
+      <c r="H20" s="17">
         <f>AVERAGE((H17-I$3)/I$3,(H18-I$3)/I$3,(H19-I$3)/I$3)</f>
         <v>10.74698207971027</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="17">
         <f>AVERAGE(I17:I19)</f>
         <v>0.25459999999999999</v>
       </c>
-      <c r="J20" s="18">
+      <c r="J20" s="17">
         <f>AVERAGE((J17-K$3)/K$3,(J18-K$3)/K$3,(J19-K$3)/K$3)</f>
         <v>23.887189735854893</v>
       </c>
-      <c r="K20" s="19">
+      <c r="K20" s="17">
         <f>AVERAGE(K17:K19)</f>
         <v>11.830666666666666</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="17">
         <f>STDEV((B17-C$3)/C$3,(B18-C$3)/C$3,(B19-C$3)/C$3)</f>
         <v>0.49059549839620331</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="17">
         <f>STDEV(C17:C19)</f>
         <v>0.38783013034059133</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="17">
         <f>STDEV((D17-E$3)/E$3,(D18-E$3)/E$3,(D19-E$3)/E$3)</f>
         <v>0.2229196853687416</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="17">
         <f>STDEV(E17:E19)</f>
         <v>3.8682468035704833E-3</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="17">
         <f>STDEV((F17-G$3)/G$3,(F18-G$3)/G$3,(F19-G$3)/G$3)</f>
         <v>0.54848266400633539</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="17">
         <f>STDEV(G17:G19)</f>
         <v>63437956.749087222</v>
       </c>
-      <c r="H21" s="19">
+      <c r="H21" s="17">
         <f>STDEV((H17-I$3)/I$3,(H18-I$3)/I$3,(H19-I$3)/I$3)</f>
         <v>1.3223047688377811</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="17">
         <f>STDEV(I17:I19)</f>
         <v>5.0089919145472651E-3</v>
       </c>
-      <c r="J21" s="19">
+      <c r="J21" s="17">
         <f>STDEV((J17-K$3)/K$3,(J18-K$3)/K$3,(J19-K$3)/K$3)</f>
         <v>0.15735877283524133</v>
       </c>
-      <c r="K21" s="19">
+      <c r="K21" s="17">
         <f>STDEV(K17:K19)</f>
         <v>0.94688272417091524</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="36"/>
+      <c r="D23" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="36"/>
+      <c r="F23" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="36"/>
+      <c r="H23" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="24"/>
-      <c r="D23" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="24"/>
-      <c r="F23" s="23" t="s">
+      <c r="I23" s="36"/>
+      <c r="J23" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23" s="36"/>
+    </row>
+    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="13">
+        <v>280</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E24" s="13">
+        <v>130</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G24" s="13">
+        <v>18512</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="I24" s="13">
+        <v>144</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="K24" s="13">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="32"/>
+      <c r="B25" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="24"/>
-      <c r="H23" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="24"/>
-      <c r="J23" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K23" s="24"/>
-    </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="14">
-        <v>280</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="E24" s="14">
-        <v>130</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="G24" s="14">
-        <v>18512</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="I24" s="14">
-        <v>144</v>
-      </c>
-      <c r="J24" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="K24" s="14">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="22"/>
-      <c r="B25" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" s="27">
+      <c r="C25" s="33">
         <v>2579</v>
       </c>
-      <c r="D25" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="27">
+      <c r="D25" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="33">
         <v>6110</v>
       </c>
-      <c r="F25" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="27">
+      <c r="F25" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="33">
         <v>645238</v>
       </c>
-      <c r="H25" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="I25" s="27">
+      <c r="H25" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="33">
         <v>58537</v>
       </c>
-      <c r="J25" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="K25" s="27">
+      <c r="J25" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" s="33">
         <v>224094</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
+      <c r="A26" s="32"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="22"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="21"/>
-      <c r="K27" s="22"/>
+      <c r="A27" s="32"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="32"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="22"/>
-      <c r="B28" s="16" t="s">
+      <c r="A28" s="32"/>
+      <c r="B28" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F28" s="16" t="s">
+      <c r="F28" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="G28" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H28" s="16" t="s">
+      <c r="H28" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="I28" s="15" t="s">
+      <c r="I28" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J28" s="16" t="s">
+      <c r="J28" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="K28" s="15" t="s">
+      <c r="K28" s="14" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B29" s="17">
-        <v>13636.36</v>
-      </c>
-      <c r="C29" s="17">
-        <v>9.5574999999999992</v>
-      </c>
-      <c r="D29" s="17">
-        <v>14260.8</v>
-      </c>
-      <c r="E29" s="17">
-        <v>6.3170999999999999</v>
-      </c>
-      <c r="F29" s="17">
-        <v>51394136.049999997</v>
-      </c>
-      <c r="G29" s="17">
-        <v>173436.6257</v>
-      </c>
-      <c r="H29" s="17">
-        <v>225651.23</v>
-      </c>
-      <c r="I29" s="17">
-        <v>10.911899999999999</v>
-      </c>
-      <c r="J29" s="17">
-        <v>3483130.73</v>
-      </c>
-      <c r="K29" s="17">
-        <v>34.001399999999997</v>
+      <c r="B29" s="16">
+        <v>7084.77</v>
+      </c>
+      <c r="C29" s="16">
+        <v>110.23739999999999</v>
+      </c>
+      <c r="D29" s="16">
+        <v>11678.97</v>
+      </c>
+      <c r="E29" s="16">
+        <v>14.079599999999999</v>
+      </c>
+      <c r="F29" s="16">
+        <v>44338773.340000004</v>
+      </c>
+      <c r="G29" s="16">
+        <v>162846.98819999999</v>
+      </c>
+      <c r="H29" s="16">
+        <v>191420.62</v>
+      </c>
+      <c r="I29" s="16">
+        <v>18.5349</v>
+      </c>
+      <c r="J29" s="16">
+        <v>946937.14</v>
+      </c>
+      <c r="K29" s="16">
+        <v>2224.7725</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="17">
-        <v>13178.49</v>
-      </c>
-      <c r="C30" s="17">
-        <v>9.2847000000000008</v>
-      </c>
-      <c r="D30" s="17">
-        <v>15545.3</v>
-      </c>
-      <c r="E30" s="17">
-        <v>7.1111000000000004</v>
-      </c>
-      <c r="F30" s="17">
-        <v>50743744.5</v>
-      </c>
-      <c r="G30" s="17">
-        <v>164031.9927</v>
-      </c>
-      <c r="H30" s="17">
-        <v>265243.32</v>
-      </c>
-      <c r="I30" s="17">
-        <v>14.889200000000001</v>
-      </c>
-      <c r="J30" s="17">
-        <v>3401755.73</v>
-      </c>
-      <c r="K30" s="17">
-        <v>43.829000000000001</v>
+      <c r="B30" s="16">
+        <v>6905.74</v>
+      </c>
+      <c r="C30" s="16">
+        <v>73.062899999999999</v>
+      </c>
+      <c r="D30" s="16">
+        <v>10536.46</v>
+      </c>
+      <c r="E30" s="16">
+        <v>12.854100000000001</v>
+      </c>
+      <c r="F30" s="16">
+        <v>43481569.539999999</v>
+      </c>
+      <c r="G30" s="16">
+        <v>238787.73209999999</v>
+      </c>
+      <c r="H30" s="16">
+        <v>200757.01</v>
+      </c>
+      <c r="I30" s="16">
+        <v>15.8529</v>
+      </c>
+      <c r="J30" s="16">
+        <v>836580.93</v>
+      </c>
+      <c r="K30" s="16">
+        <v>2348.5772999999999</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="17">
-        <v>14191.92</v>
-      </c>
-      <c r="C31" s="17">
-        <v>6.4379999999999997</v>
-      </c>
-      <c r="D31" s="17">
-        <v>16510.27</v>
-      </c>
-      <c r="E31" s="17">
-        <v>6.0346000000000002</v>
-      </c>
-      <c r="F31" s="17">
-        <v>50962909.799999997</v>
-      </c>
-      <c r="G31" s="17">
-        <v>182635.92929999999</v>
-      </c>
-      <c r="H31" s="17">
-        <v>277422.81</v>
-      </c>
-      <c r="I31" s="17">
-        <v>17.801300000000001</v>
-      </c>
-      <c r="J31" s="17">
-        <v>3538871.8</v>
-      </c>
-      <c r="K31" s="17">
-        <v>40.497799999999998</v>
+      <c r="B31" s="16">
+        <v>7023.88</v>
+      </c>
+      <c r="C31" s="16">
+        <v>119.3869</v>
+      </c>
+      <c r="D31" s="16">
+        <v>12574.8</v>
+      </c>
+      <c r="E31" s="16">
+        <v>11.6661</v>
+      </c>
+      <c r="F31" s="16">
+        <v>43718362.030000001</v>
+      </c>
+      <c r="G31" s="16">
+        <v>239844.1906</v>
+      </c>
+      <c r="H31" s="16">
+        <v>187879.03</v>
+      </c>
+      <c r="I31" s="16">
+        <v>16.232299999999999</v>
+      </c>
+      <c r="J31" s="16">
+        <v>898358.86</v>
+      </c>
+      <c r="K31" s="16">
+        <v>2024.0343</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="17">
         <f>AVERAGE((B29-C$3)/C$3,(B30-C$3)/C$3,(B31-C$3)/C$3)</f>
-        <v>4.3000865968721724</v>
-      </c>
-      <c r="C32" s="19">
+        <v>1.7160902158459352</v>
+      </c>
+      <c r="C32" s="17">
         <f>AVERAGE(C29:C31)</f>
-        <v>8.426733333333333</v>
-      </c>
-      <c r="D32" s="18">
+        <v>100.89573333333333</v>
+      </c>
+      <c r="D32" s="19">
         <f>AVERAGE((D29-E$3)/E$3,(D30-E$3)/E$3,(D31-E$3)/E$3)</f>
-        <v>1.5268068739770868</v>
-      </c>
-      <c r="E32" s="19">
+        <v>0.89799399890889242</v>
+      </c>
+      <c r="E32" s="17">
         <f>AVERAGE(E29:E31)</f>
-        <v>6.4876000000000005</v>
-      </c>
-      <c r="F32" s="18">
+        <v>12.8666</v>
+      </c>
+      <c r="F32" s="17">
         <f>AVERAGE((F29-G$3)/G$3,(F30-G$3)/G$3,(F31-G$3)/G$3)</f>
-        <v>78.09267089559718</v>
-      </c>
-      <c r="G32" s="19">
+        <v>66.953584522300289</v>
+      </c>
+      <c r="G32" s="17">
         <f>AVERAGE(G29:G31)</f>
-        <v>173368.18256666666</v>
-      </c>
-      <c r="H32" s="18">
+        <v>213826.30363333333</v>
+      </c>
+      <c r="H32" s="17">
         <f>AVERAGE((H29-I$3)/I$3,(H30-I$3)/I$3,(H31-I$3)/I$3)</f>
-        <v>3.3751095318630386</v>
-      </c>
-      <c r="I32" s="19">
+        <v>2.3030770282043838</v>
+      </c>
+      <c r="I32" s="17">
         <f>AVERAGE(I29:I31)</f>
-        <v>14.534133333333335</v>
-      </c>
-      <c r="J32" s="18">
+        <v>16.873366666666666</v>
+      </c>
+      <c r="J32" s="17">
         <f>AVERAGE((J29-K$3)/K$3,(J30-K$3)/K$3,(J31-K$3)/K$3)</f>
-        <v>14.505038451126163</v>
-      </c>
-      <c r="K32" s="19">
+        <v>2.9892142434276097</v>
+      </c>
+      <c r="K32" s="17">
         <f>AVERAGE(K29:K31)</f>
-        <v>39.442733333333329</v>
+        <v>2199.1280333333334</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B33" s="19">
+      <c r="B33" s="17">
         <f>STDEV((B29-C$3)/C$3,(B30-C$3)/C$3,(B31-C$3)/C$3)</f>
-        <v>0.19678136186461742</v>
-      </c>
-      <c r="C33" s="19">
+        <v>3.5295784333622744E-2</v>
+      </c>
+      <c r="C33" s="17">
         <f>STDEV(C29:C31)</f>
-        <v>1.7276863613901003</v>
-      </c>
-      <c r="D33" s="19">
+        <v>24.534227032522114</v>
+      </c>
+      <c r="D33" s="17">
         <f>STDEV((D29-E$3)/E$3,(D30-E$3)/E$3,(D31-E$3)/E$3)</f>
-        <v>0.18469902004665073</v>
-      </c>
-      <c r="E33" s="19">
+        <v>0.16721026838591455</v>
+      </c>
+      <c r="E33" s="17">
         <f>STDEV(E29:E31)</f>
-        <v>0.55813596013874633</v>
-      </c>
-      <c r="F33" s="19">
+        <v>1.2067985540263126</v>
+      </c>
+      <c r="F33" s="17">
         <f>STDEV((F29-G$3)/G$3,(F30-G$3)/G$3,(F31-G$3)/G$3)</f>
-        <v>0.51284566107356222</v>
-      </c>
-      <c r="G33" s="19">
+        <v>0.68606826483167627</v>
+      </c>
+      <c r="G33" s="17">
         <f>STDEV(G29:G31)</f>
-        <v>9302.157147730848</v>
-      </c>
-      <c r="H33" s="19">
+        <v>44152.542142882594</v>
+      </c>
+      <c r="H33" s="17">
         <f>STDEV((H29-I$3)/I$3,(H30-I$3)/I$3,(H31-I$3)/I$3)</f>
-        <v>0.46241419329654254</v>
-      </c>
-      <c r="I33" s="19">
+        <v>0.11365010787779832</v>
+      </c>
+      <c r="I33" s="17">
         <f>STDEV(I29:I31)</f>
-        <v>3.4583973663148275</v>
-      </c>
-      <c r="J33" s="19">
+        <v>1.451380671406828</v>
+      </c>
+      <c r="J33" s="17">
         <f>STDEV((J29-K$3)/K$3,(J30-K$3)/K$3,(J31-K$3)/K$3)</f>
-        <v>0.3077112064957051</v>
-      </c>
-      <c r="K33" s="19">
+        <v>0.24681390607901385</v>
+      </c>
+      <c r="K33" s="17">
         <f>STDEV(K29:K31)</f>
-        <v>4.998030081275366</v>
+        <v>163.78421387671438</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A34" s="4"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A46" s="4" t="s">
+    <row r="36" spans="1:11" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B36" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="K36" s="30"/>
+    </row>
+    <row r="37" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" s="13">
+        <v>280</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E37" s="13">
+        <v>130</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G37" s="13">
+        <v>18512</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="I37" s="13">
+        <v>144</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="K37" s="13">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="28"/>
+      <c r="B38" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="21">
+        <v>2579</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38" s="21">
+        <v>6110</v>
+      </c>
+      <c r="F38" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" s="21">
+        <v>645238</v>
+      </c>
+      <c r="H38" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" s="21">
+        <v>58537</v>
+      </c>
+      <c r="J38" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="21">
+        <v>224094</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A39" s="28"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="26"/>
+      <c r="K39" s="22"/>
+    </row>
+    <row r="40" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="28"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="23"/>
+      <c r="K40" s="24"/>
+    </row>
+    <row r="41" spans="1:11" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="29"/>
+      <c r="B41" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="J41" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="16">
+        <v>4011.24</v>
+      </c>
+      <c r="C42" s="16">
+        <v>48811.027999999998</v>
+      </c>
+      <c r="D42" s="16">
+        <v>7705.49</v>
+      </c>
+      <c r="E42" s="16">
+        <v>19133.572100000001</v>
+      </c>
+      <c r="F42" s="16">
+        <v>40777561.030000001</v>
+      </c>
+      <c r="G42" s="16">
+        <v>348720.7365</v>
+      </c>
+      <c r="H42" s="16">
+        <v>128041.93</v>
+      </c>
+      <c r="I42" s="16">
+        <v>27565.896700000001</v>
+      </c>
+      <c r="J42" s="16">
+        <v>1117449.31</v>
+      </c>
+      <c r="K42" s="16">
+        <v>150180.9607</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="16">
+        <v>3918.1</v>
+      </c>
+      <c r="C43" s="16">
+        <v>71920.957999999999</v>
+      </c>
+      <c r="D43" s="16">
+        <v>9194.25</v>
+      </c>
+      <c r="E43" s="16">
+        <v>17880.0671</v>
+      </c>
+      <c r="F43" s="16">
+        <v>44504055.590000004</v>
+      </c>
+      <c r="G43" s="16">
+        <v>351875.22169999999</v>
+      </c>
+      <c r="H43" s="16">
+        <v>94218.25</v>
+      </c>
+      <c r="I43" s="16">
+        <v>26049.9375</v>
+      </c>
+      <c r="J43" s="16">
+        <v>889271.8</v>
+      </c>
+      <c r="K43" s="16">
+        <v>160550.22719999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="16">
+        <v>4457.49</v>
+      </c>
+      <c r="C44" s="16">
+        <v>46729.837899999999</v>
+      </c>
+      <c r="D44" s="16">
+        <v>8647.64</v>
+      </c>
+      <c r="E44" s="16">
+        <v>17832.952300000001</v>
+      </c>
+      <c r="F44" s="16">
+        <v>39122087.469999999</v>
+      </c>
+      <c r="G44" s="16">
+        <v>140101.75750000001</v>
+      </c>
+      <c r="H44" s="16">
+        <v>150536.89000000001</v>
+      </c>
+      <c r="I44" s="16">
+        <v>23834.6338</v>
+      </c>
+      <c r="J44" s="16">
+        <v>853982.55</v>
+      </c>
+      <c r="K44" s="16">
+        <v>179041.1777</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" s="17">
+        <f>AVERAGE((B42-C$3)/C$3,(B43-C$3)/C$3,(B44-C$3)/C$3)</f>
+        <v>0.60098617035026491</v>
+      </c>
+      <c r="C45" s="17">
+        <f>AVERAGE(C42:C44)</f>
+        <v>55820.60796666667</v>
+      </c>
+      <c r="D45" s="19">
+        <f>AVERAGE((D42-E$3)/E$3,(D43-E$3)/E$3,(D44-E$3)/E$3)</f>
+        <v>0.39374686306601198</v>
+      </c>
+      <c r="E45" s="17">
+        <f>AVERAGE(E42:E44)</f>
+        <v>18282.197166666669</v>
+      </c>
+      <c r="F45" s="17">
+        <f>AVERAGE((F42-G$3)/G$3,(F43-G$3)/G$3,(F44-G$3)/G$3)</f>
+        <v>63.26760569484955</v>
+      </c>
+      <c r="G45" s="17">
+        <f>AVERAGE(G42:G44)</f>
+        <v>280232.57190000004</v>
+      </c>
+      <c r="H45" s="17">
+        <f>AVERAGE((H42-I$3)/I$3,(H43-I$3)/I$3,(H44-I$3)/I$3)</f>
+        <v>1.122857167261732</v>
+      </c>
+      <c r="I45" s="17">
+        <f>AVERAGE(I42:I44)</f>
+        <v>25816.822666666663</v>
+      </c>
+      <c r="J45" s="17">
+        <f>AVERAGE((J42-K$3)/K$3,(J43-K$3)/K$3,(J44-K$3)/K$3)</f>
+        <v>3.2552138239607782</v>
+      </c>
+      <c r="K45" s="17">
+        <f>AVERAGE(K42:K44)</f>
+        <v>163257.4552</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="17">
+        <f>STDEV((B42-C$3)/C$3,(B43-C$3)/C$3,(B44-C$3)/C$3)</f>
+        <v>0.11179360631818584</v>
+      </c>
+      <c r="C46" s="17">
+        <f>STDEV(C42:C44)</f>
+        <v>13982.088236560949</v>
+      </c>
+      <c r="D46" s="17">
+        <f>STDEV((D42-E$3)/E$3,(D43-E$3)/E$3,(D44-E$3)/E$3)</f>
+        <v>0.1232547425741701</v>
+      </c>
+      <c r="E46" s="17">
+        <f>STDEV(E42:E44)</f>
+        <v>737.68855821817783</v>
+      </c>
+      <c r="F46" s="17">
+        <f>STDEV((F42-G$3)/G$3,(F43-G$3)/G$3,(F44-G$3)/G$3)</f>
+        <v>4.2722161247194768</v>
+      </c>
+      <c r="G46" s="17">
+        <f>STDEV(G42:G44)</f>
+        <v>121367.0941916493</v>
+      </c>
+      <c r="H46" s="17">
+        <f>STDEV((H42-I$3)/I$3,(H43-I$3)/I$3,(H44-I$3)/I$3)</f>
+        <v>0.48428490359072873</v>
+      </c>
+      <c r="I46" s="17">
+        <f>STDEV(I42:I44)</f>
+        <v>1876.5227420335534</v>
+      </c>
+      <c r="J46" s="17">
+        <f>STDEV((J42-K$3)/K$3,(J43-K$3)/K$3,(J44-K$3)/K$3)</f>
+        <v>0.63820578835418895</v>
+      </c>
+      <c r="K46" s="17">
+        <f>STDEV(K42:K44)</f>
+        <v>14619.331171594695</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" spans="1:13" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A50" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="49" spans="1:13" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="32"/>
-      <c r="B49" s="34" t="s">
+    <row r="51" spans="1:13" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="1:13" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="53" spans="1:13" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="42"/>
+      <c r="B53" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="45"/>
+      <c r="D53" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="38"/>
+      <c r="F53" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="45"/>
+      <c r="H53" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="35"/>
-      <c r="D49" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" s="29"/>
-      <c r="F49" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="G49" s="35"/>
-      <c r="H49" s="28" t="s">
+      <c r="I53" s="38"/>
+      <c r="J53" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="I49" s="29"/>
-      <c r="J49" s="28" t="s">
+      <c r="K53" s="38"/>
+      <c r="L53" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="M53" s="40"/>
+    </row>
+    <row r="54" spans="1:13" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="43"/>
+      <c r="B54" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="K49" s="29"/>
-      <c r="L49" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="M49" s="31"/>
-    </row>
-    <row r="50" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="33"/>
-      <c r="B50" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D50" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E50" s="2" t="s">
+      <c r="D54" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F50" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G50" s="1" t="s">
+      <c r="F54" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H50" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I50" s="2" t="s">
+      <c r="H54" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I54" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="J50" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K50" s="2" t="s">
+      <c r="J54" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K54" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L50" s="5" t="s">
+      <c r="L54" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M50" s="6" t="s">
+      <c r="M54" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="7" t="s">
+    <row r="55" spans="1:13" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B51" s="3">
-        <f t="shared" ref="B51:K51" si="0">B8</f>
+      <c r="B55" s="3">
+        <f t="shared" ref="B55:K55" si="0">B8</f>
         <v>10.747506785575805</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C55" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D55" s="3">
         <f t="shared" si="0"/>
         <v>5.6116972176759417</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E55" s="3">
         <f t="shared" si="0"/>
         <v>0.99399999999999999</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F55" s="3">
         <f t="shared" si="0"/>
         <v>78.291188383201245</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G55" s="3">
         <f t="shared" si="0"/>
         <v>234665.56880000001</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H55" s="3">
         <f t="shared" si="0"/>
         <v>9.9464249961562778</v>
       </c>
-      <c r="I51" s="3">
+      <c r="I55" s="3">
         <f t="shared" si="0"/>
         <v>0.30349999999999999</v>
       </c>
-      <c r="J51" s="3">
+      <c r="J55" s="3">
         <f t="shared" si="0"/>
         <v>24.302170026863728</v>
       </c>
-      <c r="K51" s="3">
+      <c r="K55" s="3">
         <f t="shared" si="0"/>
         <v>15.7926</v>
       </c>
-      <c r="L51" s="8">
-        <f>AVERAGE(B51,D51,F51,H51,J51)</f>
+      <c r="L55" s="8">
+        <f t="shared" ref="L55:M58" si="1">AVERAGE(B55,D55,F55,H55,J55)</f>
         <v>25.779797481894597</v>
       </c>
-      <c r="M51" s="8">
-        <f>AVERAGE(C51,E51,G51,I51,K51)</f>
+      <c r="M55" s="8">
+        <f t="shared" si="1"/>
         <v>46936.531780000005</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B52" s="3">
-        <f t="shared" ref="B52:K52" si="1">B20</f>
+    <row r="56" spans="1:13" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B56" s="3">
+        <f t="shared" ref="B56:K56" si="2">B20</f>
         <v>11.095469820343803</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C56" s="3">
+        <f t="shared" si="2"/>
+        <v>1.0012999999999999</v>
+      </c>
+      <c r="D56" s="3">
+        <f t="shared" si="2"/>
+        <v>5.957828696126569</v>
+      </c>
+      <c r="E56" s="3">
+        <f t="shared" si="2"/>
+        <v>0.20926666666666668</v>
+      </c>
+      <c r="F56" s="3">
+        <f t="shared" si="2"/>
+        <v>78.450836115252557</v>
+      </c>
+      <c r="G56" s="3">
+        <f t="shared" si="2"/>
+        <v>36736612.294666663</v>
+      </c>
+      <c r="H56" s="3">
+        <f t="shared" si="2"/>
+        <v>10.74698207971027</v>
+      </c>
+      <c r="I56" s="3">
+        <f t="shared" si="2"/>
+        <v>0.25459999999999999</v>
+      </c>
+      <c r="J56" s="3">
+        <f t="shared" si="2"/>
+        <v>23.887189735854893</v>
+      </c>
+      <c r="K56" s="3">
+        <f t="shared" si="2"/>
+        <v>11.830666666666666</v>
+      </c>
+      <c r="L56" s="8">
         <f t="shared" si="1"/>
-        <v>1.0012999999999999</v>
-      </c>
-      <c r="D52" s="3">
+        <v>26.027661289457619</v>
+      </c>
+      <c r="M56" s="8" t="b">
+        <f>B28=AVERAGE(C56,E56,G56,I56,K56)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B57" s="10">
+        <f>B32</f>
+        <v>1.7160902158459352</v>
+      </c>
+      <c r="C57" s="10">
+        <f>C32</f>
+        <v>100.89573333333333</v>
+      </c>
+      <c r="D57" s="10">
+        <f>D8</f>
+        <v>5.6116972176759417</v>
+      </c>
+      <c r="E57" s="10">
+        <f>E32</f>
+        <v>12.8666</v>
+      </c>
+      <c r="F57" s="10">
+        <f>F32</f>
+        <v>66.953584522300289</v>
+      </c>
+      <c r="G57" s="10">
+        <f>G32</f>
+        <v>213826.30363333333</v>
+      </c>
+      <c r="H57" s="10">
+        <f>H32</f>
+        <v>2.3030770282043838</v>
+      </c>
+      <c r="I57" s="10">
+        <f>H32</f>
+        <v>2.3030770282043838</v>
+      </c>
+      <c r="J57" s="10">
+        <f>J32</f>
+        <v>2.9892142434276097</v>
+      </c>
+      <c r="K57" s="10">
+        <f>K32</f>
+        <v>2199.1280333333334</v>
+      </c>
+      <c r="L57" s="8">
         <f t="shared" si="1"/>
-        <v>5.957828696126569</v>
-      </c>
-      <c r="E52" s="3">
+        <v>15.914732645490833</v>
+      </c>
+      <c r="M57" s="9">
         <f t="shared" si="1"/>
-        <v>0.20926666666666668</v>
-      </c>
-      <c r="F52" s="3">
+        <v>43228.299415405643</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B58" s="10">
+        <f t="shared" ref="B58:K58" si="3">B45</f>
+        <v>0.60098617035026491</v>
+      </c>
+      <c r="C58" s="10">
+        <f t="shared" si="3"/>
+        <v>55820.60796666667</v>
+      </c>
+      <c r="D58" s="10">
+        <f t="shared" si="3"/>
+        <v>0.39374686306601198</v>
+      </c>
+      <c r="E58" s="10">
+        <f t="shared" si="3"/>
+        <v>18282.197166666669</v>
+      </c>
+      <c r="F58" s="10">
+        <f t="shared" si="3"/>
+        <v>63.26760569484955</v>
+      </c>
+      <c r="G58" s="10">
+        <f t="shared" si="3"/>
+        <v>280232.57190000004</v>
+      </c>
+      <c r="H58" s="10">
+        <f t="shared" si="3"/>
+        <v>1.122857167261732</v>
+      </c>
+      <c r="I58" s="10">
+        <f t="shared" si="3"/>
+        <v>25816.822666666663</v>
+      </c>
+      <c r="J58" s="10">
+        <f t="shared" si="3"/>
+        <v>3.2552138239607782</v>
+      </c>
+      <c r="K58" s="10">
+        <f t="shared" si="3"/>
+        <v>163257.4552</v>
+      </c>
+      <c r="L58" s="8">
         <f t="shared" si="1"/>
-        <v>78.450836115252557</v>
-      </c>
-      <c r="G52" s="3">
+        <v>13.728081943897667</v>
+      </c>
+      <c r="M58" s="9">
         <f t="shared" si="1"/>
-        <v>36736612.294666663</v>
-      </c>
-      <c r="H52" s="3">
-        <f t="shared" si="1"/>
-        <v>10.74698207971027</v>
-      </c>
-      <c r="I52" s="3">
-        <f t="shared" si="1"/>
-        <v>0.25459999999999999</v>
-      </c>
-      <c r="J52" s="3">
-        <f t="shared" si="1"/>
-        <v>23.887189735854893</v>
-      </c>
-      <c r="K52" s="3">
-        <f t="shared" si="1"/>
-        <v>11.830666666666666</v>
-      </c>
-      <c r="L52" s="8">
-        <f>AVERAGE(B52,D52,F52,H52,J52)</f>
-        <v>26.027661289457619</v>
-      </c>
-      <c r="M52" s="8">
-        <f>AVERAGE(C52,E52,G52,I52,K52)</f>
-        <v>7347325.1181000005</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="11"/>
-      <c r="J53" s="11"/>
-      <c r="K53" s="11"/>
-      <c r="L53" s="8"/>
-      <c r="M53" s="9"/>
-    </row>
-    <row r="54" spans="1:13" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="11"/>
-      <c r="J54" s="11"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="8"/>
-      <c r="M54" s="9"/>
-    </row>
-    <row r="55" spans="1:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="56" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+        <v>108681.93098000002</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="60" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="61" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2945,12 +3461,13 @@
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="70">
+  <mergeCells count="91">
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="K13:K14"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -2963,18 +3480,23 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="A12:A16"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="L53:M53"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="H5:I5"/>
@@ -2989,14 +3511,6 @@
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="G13:G14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="J13:J14"/>
@@ -3004,18 +3518,41 @@
     <mergeCell ref="J27:K27"/>
     <mergeCell ref="H23:I23"/>
     <mergeCell ref="J23:K23"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="E25:E26"/>
     <mergeCell ref="F25:F26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="J38:J39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
